--- a/daily_matches/job_matches_2026-04-01.xlsx
+++ b/daily_matches/job_matches_2026-04-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sr. AI/ML Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Commence</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.8</v>
+        <v>14.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, LangChain, RAG, S3, MLflow, FastAPI, Docker, Kubernetes, CI/CD</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Databricks, Python</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,462 +496,252 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a29e442792da77f5</t>
+          <t>https://www.indeed.com/viewjob?jk=9ff787e7518e81a0</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Software Engineer, Community</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Quizlet</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.8</v>
+        <v>13.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, TensorFlow, PyTorch, Docker, Kubernetes, Git, Kafka, Hadoop, NoSQL, Tableau</t>
+          <t>Data Scientist, Generative AI, RAG, BigQuery, Docker, Kubernetes, CI/CD, BigQuery, MySQL, SQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07f27194308ee9cd</t>
+          <t>https://www.indeed.com/viewjob?jk=304492ee985c639a</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Senior Full Stack Engineer- TypeScript/Node</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Transamerica</t>
+          <t>Egen Solutions Inc</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Cedar Rapids, IA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>12.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Kinesis, Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, PostgreSQL, MySQL, MongoDB, NoSQL, SQL, R</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6228a15683ca91c</t>
+          <t>https://www.indeed.com/viewjob?jk=94ea42d7080157de</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>GCP AI Engineer - Cambridge, MA</t>
+          <t>Software Engineer III - Data Engineering and MLOps</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Lumeris</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.6</v>
+        <v>10</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Gemini, BigQuery, Dataflow, Docker, Kubernetes, Terraform</t>
+          <t>RAG, Data Lake, CI/CD, Databricks, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa76078529e44025</t>
+          <t>https://www.indeed.com/viewjob?jk=b03dda01cdd909ce</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Branch Channel Generative AI - Applied AI ML Senior Associate</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>employers</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>10</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Apache Airflow, CI/CD, Git, Databricks, PySpark, Power BI, Quicksight, Python, SQL</t>
+          <t>Generative AI, RAG, TensorFlow, PyTorch, Git, Python, R, Java, Optimization</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87490bb4a381dfbc</t>
+          <t>https://www.indeed.com/viewjob?jk=3032eaf1b64c9634</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Test Automation Engineer / SDET - HYBRID</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL, R</t>
+          <t>LangChain, RAG, Prompt Engineering, Kubernetes, CI/CD, Git, R, Java, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3302c4147ab0b0cf</t>
+          <t>https://www.indeed.com/viewjob?jk=438fdc5ed57d2861</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack, UI</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Berkshire Grey</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bedford, MA, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka, MongoDB, NoSQL, Python, SQL</t>
+          <t>LangChain, RAG, Prompt Engineering, Kubernetes, CI/CD, Git, R, Java, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb7e0f7f9512c459</t>
+          <t>https://www.indeed.com/viewjob?jk=8d8cc9c84850a48e</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Python Snowflake Data Engineer - ONSITE</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Git, Snowflake, PostgreSQL, Power BI, Python, SQL, R</t>
+          <t>LangChain, RAG, Prompt Engineering, Kubernetes, CI/CD, Git, R, Java, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d484f254d7720016</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Technology Engineer (Java GoLang Full Stack/UI)</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>PNC Financial Services Group</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Pittsburgh, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>RAG, Kubernetes, CI/CD, Jenkins, Kafka, MySQL, NoSQL, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=23c5e6b5f589d4d1</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Analyst - Data Analytics Digital Lounge Services</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>American Express</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>RAG, BigQuery, Git, BigQuery, Tableau, Python, SQL, R, Scala, A/B Testing</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c7ae42777ddb1cf6</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Quality Assurance Engineer</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>GNC</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Pittsburgh, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>10</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, CI/CD, Git, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=574bd3ca5a3cfe30</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Sr. Software Engineer - Ignition</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>KPMG</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Montvale, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>10</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, AKS, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e55796fe072aa5b8</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>HR Analytics Data Scientist</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>KLA</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ann Arbor, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>10</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Copilot, XGBoost, Git, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b2d1c5db4af0bdde</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Senior Cloud Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Eli Lilly</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>10</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>RAG, S3, EC2, CI/CD, Jenkins, GitHub Actions, Git, R, Scala</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ec8f244e5c12367a</t>
+          <t>https://www.indeed.com/viewjob?jk=aaf3574230dbf0f6</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-01.xlsx
+++ b/daily_matches/job_matches_2026-04-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>GenAI Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>14.4</v>
+        <v>18.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Databricks, Python</t>
+          <t>AI Engineer, Data Scientist, RAG, Azure ML, MLflow, Docker, Kubernetes, AKS, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,67 +496,67 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ff787e7518e81a0</t>
+          <t>https://www.indeed.com/viewjob?jk=083ee0db6cfdce14</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Community</t>
+          <t>ML Infrastructure Architect</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Quizlet</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13.3</v>
+        <v>17.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, BigQuery, Docker, Kubernetes, CI/CD, BigQuery, MySQL, SQL</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, FastAPI, Docker</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=304492ee985c639a</t>
+          <t>https://www.indeed.com/viewjob?jk=0274f1883c773429</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer- TypeScript/Node</t>
+          <t>CrowdStrike AI Security Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Egen Solutions Inc</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, PostgreSQL, MySQL, MongoDB, NoSQL, SQL, R</t>
+          <t>LangChain, RAG, FAISS, Pinecone, TensorFlow, PyTorch, XGBoost, LightGBM, MLflow, FastAPI</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94ea42d7080157de</t>
+          <t>https://www.indeed.com/viewjob?jk=073d98524d049213</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer III - Data Engineering and MLOps</t>
+          <t>Senior Java Software Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>YO IT CONSULTING</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, CI/CD, Databricks, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Copilot, EC2, Data Lake, Kubernetes, CI/CD, Git, Kafka, NoSQL, SQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b03dda01cdd909ce</t>
+          <t>https://www.indeed.com/viewjob?jk=2bea7326a4970d38</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Branch Channel Generative AI - Applied AI ML Senior Associate</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>YO IT CONSULTING</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, TensorFlow, PyTorch, Git, Python, R, Java, Optimization</t>
+          <t>RAG, Copilot, EC2, Data Lake, Kubernetes, CI/CD, Git, Kafka, NoSQL, SQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3032eaf1b64c9634</t>
+          <t>https://www.indeed.com/viewjob?jk=7b588911fd6c0bd0</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr Java Developer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>YO IT CONSULTING</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Prompt Engineering, Kubernetes, CI/CD, Git, R, Java, Scala</t>
+          <t>RAG, Copilot, EC2, Data Lake, Kubernetes, CI/CD, Git, Kafka, NoSQL, SQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=438fdc5ed57d2861</t>
+          <t>https://www.indeed.com/viewjob?jk=5e2143304ae215ab</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr Java Backend Developer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>YO IT CONSULTING</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Prompt Engineering, Kubernetes, CI/CD, Git, R, Java, Scala</t>
+          <t>RAG, Copilot, EC2, Data Lake, Kubernetes, CI/CD, Git, Kafka, NoSQL, SQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,42 +706,742 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d8cc9c84850a48e</t>
+          <t>https://www.indeed.com/viewjob?jk=0b81d52c01d7856d</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Machine Learning Threat Intelligence Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, TensorFlow, PyTorch, FastAPI, Docker, Kubernetes, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6db760ee05781078</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>AWS Cloud Site Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Basking Ridge, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>RAG, S3, Athena, Kubernetes, CI/CD, GitHub Actions, Git, Hadoop, Python, R</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6e47569360256c27</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Test Automation Engineer / SDET - HYBRID</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4ab801d158b6cd6f</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Munich Re</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, MLflow, Docker, CI/CD, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9867eee729f1fe15</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>GenAI Threat Intelligence Analyst</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Prompt Engineering, CI/CD, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=52f7c0f76c12cf7d</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Machine Learning Threat Intelligence Engineer</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Data Scientist, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Hadoop, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=71b08a308d9c4e4a</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Junior Go/Typescript Developer (AI Assisted)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, S3, EC2, Docker, CI/CD, GitHub Actions, Terraform, Git, Python</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=385e3dcc63cd7825</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Intelligent Process Automation Software Engineer</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>OSI Systems, Inc</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Snoqualmie, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, CI/CD, Git, Power BI, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f1cf38df07620a12</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Machine Learning Threat Intelligence Engineer</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>TensorFlow, PyTorch, Data Lake, FastAPI, CI/CD, NoSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0b714ac0810b5df1</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Customer Success Engineer (US based, remote)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Fortanix</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>10</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, Git, Snowflake, MySQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ca722f91969c87a0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer I (Web Applications)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Alliance Technical Group</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>10</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>RAG, S3, CI/CD, Git, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1c58aa836e5be6e0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>10</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Data Scientist, Copilot, Docker, AKS, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dea133e15555de48</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Senior Software Developer</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Xplor Technologies</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>10</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>RAG, Gemini, Copilot, Git, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f1663c9f147eae34</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Senior Java Engineer</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>NTENT</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>10</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Data Scientist, Docker, Kubernetes, Git, Kafka, Hadoop, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4247840ea481f663</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Full Stack Software Engineer</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Near-Miss Management</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>10</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>S3, EC2, GitHub Actions, Git, PostgreSQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7b64c8d6f17e6cd5</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Machine Learning Threat Intelligence Engineer</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>OR, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, TensorFlow, PyTorch, CI/CD, Python, R, Bayesian</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7eb2bbd610da63a3</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ACCOUNT ENGINEER INTERN â€” SUMMER 2026</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Snowflake</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>10</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Prompt Engineering, Cortex, CI/CD, Snowflake, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d9d74d53ad90c74d</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Virtual Assistant 3L Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
           <t>Wells Fargo</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Chandler, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
         <v>10</v>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>LangChain, RAG, Prompt Engineering, Kubernetes, CI/CD, Git, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=aaf3574230dbf0f6</t>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, Terraform, Git, Kafka, MongoDB, R, Scala</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=82be07b07ed9819d</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Virtual Assistant 3L Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Wells Fargo</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>10</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, Terraform, Git, Kafka, MongoDB, R, Scala</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=89d26c79cb640a8f</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Virtual Assistant 3L Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Wells Fargo</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>10</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, Terraform, Git, Kafka, MongoDB, R, Scala</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1112e1be7698ce71</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Virtual Assistant 3L Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Wells Fargo</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>10</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, Terraform, Git, Kafka, MongoDB, R, Scala</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cc46955c18aac686</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-01.xlsx
+++ b/daily_matches/job_matches_2026-04-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,12 +468,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generative AI Applications Engineer (Agents &amp; RAG)</t>
+          <t>AI Engineer-Remote Opportunity</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Accenture Federal Services</t>
+          <t>Answer Financial Inc.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -482,11 +482,11 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>15.6</v>
+        <v>20</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Gemini, FAISS, Pinecone, Docker, Kubernetes, CI/CD</t>
+          <t>AI Engineer, Data Scientist, RAG, Copilot, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch, AWS SageMaker</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,19 +496,19 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59d55869b01eb667</t>
+          <t>https://www.indeed.com/viewjob?jk=f87cb2f562089112</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generative AI Applications Engineer (Agents &amp; RAG)</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Accenture Federal Services</t>
+          <t>Arkatechture</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -517,11 +517,11 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.6</v>
+        <v>18.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Gemini, FAISS, Pinecone, Docker, Kubernetes, CI/CD</t>
+          <t>Generative AI, LangChain, RAG, Prompt Engineering, Cortex, AWS SageMaker, BigQuery, Snowflake, Databricks, BigQuery</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e05e2ae4bcdb73b</t>
+          <t>https://www.indeed.com/viewjob?jk=a7028737452f8f97</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>CrowdStrike GenAI Security Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MassMutual</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.3</v>
+        <v>17.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Git, Kafka, MongoDB, NoSQL, Python, SQL, R</t>
+          <t>LangChain, RAG, Copilot, FAISS, Pinecone, Prompt Engineering, FastAPI, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4075abed317d9ce</t>
+          <t>https://www.indeed.com/viewjob?jk=55dc1ff2aee60bf8</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior AI Solutions Developer</t>
+          <t>CrowdStrike Container Security Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Riley Power Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bay City, TX, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Copilot, Hugging Face, AWS SageMaker, GCP Vertex AI, Python, SQL, R</t>
+          <t>RAG, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d3748aca7749fee</t>
+          <t>https://www.indeed.com/viewjob?jk=ec3f885a56b1d738</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AI Solutions Architect</t>
+          <t>CrowdStrike Container Security Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Riley Power Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bay City, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, Copilot, Hugging Face, AWS SageMaker, GCP Vertex AI, Git, Python, SQL, R</t>
+          <t>RAG, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0dc1c4ab21ad4c56</t>
+          <t>https://www.indeed.com/viewjob?jk=a3b70c2a3a58c840</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Intern, DevOps Engineering, Product Operations</t>
+          <t>CrowdStrike GenAI Security Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Lila Sciences</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, Tableau, Matplotlib, Seaborn</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,42 +671,952 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc473ae53e17e580</t>
+          <t>https://www.indeed.com/viewjob?jk=5294f2169087b99c</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Marketing Data Scientist</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway Direct Insurance Company</t>
+          <t>Group1001</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Zionsville, IN, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>S3, EC2, Kinesis, Docker, CI/CD, Terraform, Git, Kafka, PostgreSQL, SQL</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=328132d81f266b40</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>OpenAM</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>IN, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, LLaMA, FAISS, Prompt Engineering, FastAPI, Docker, PostgreSQL, MySQL, Python</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a2798eaba2ec3640</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, SQL, R</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b5ae44b7e644f920</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Machine Learning Threat Intelligence Engineer</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, LangChain, TensorFlow, PyTorch, MLflow, Docker, Kubernetes, CI/CD, Hadoop</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b964f7655bcd20af</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Cognos Dashboard Developer</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Synapse, FastAPI, Docker, CI/CD, Git, PostgreSQL, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fb0be82abd779045</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Cognos Dashboard Developer</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Synapse, FastAPI, Docker, CI/CD, Git, PostgreSQL, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4c35b8f5f035a5b2</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Machine Learning Threat Intelligence Engineer</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>TensorFlow, PyTorch, S3, EC2, Glue, Docker, Apache Airflow, CI/CD, Jenkins, Terraform</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=01330f2927806152</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>CrowdStrike Container Security Engineer</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NY, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Terraform, Git, Kafka, Python, R</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3927505fc5da268f</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Cloud Threat Intelligence Analyst</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>IL, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Terraform, Git, Kafka, Python, R</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=97457f1413e6a8ff</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>CrowdStrike AI Security Engineer</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NC, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, Copilot, Prompt Engineering, FastAPI, CI/CD, Git, Databricks, Python, R</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d6e92b99aa8a7b69</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>OpenAM</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NC, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, Copilot, Prompt Engineering, FastAPI, CI/CD, Git, Databricks, Python, R</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2ed4889c9b1b3b76</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Intelligence Platform Architect</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, XGBoost, MLflow, Databricks, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6109173d4b2f89d1</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist - Digital Intelligence, Device Signals</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Socure</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Carson City, NV, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, XGBoost, Git, PySpark, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8464ec9a079b1a80</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>OpenAM</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, CI/CD, Terraform, MySQL, MongoDB, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=93d9e83869d72aa4</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>OpenAM</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Prompt Engineering, TensorFlow, CI/CD, Git, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d317cc1d518716e1</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Cognos Business Intelligence Analyst</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NY, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Generative AI, Databricks, PySpark, Power BI, Python, SQL, R, Optimization, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ad29a7b3847d7779</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Cognos Business Intelligence Analyst</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NY, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Generative AI, Databricks, PySpark, Power BI, Python, SQL, R, Optimization, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=80bbbb63b208b2dd</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Senior Ad Tech Developer</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>USA TODAY Co.</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
         <v>10</v>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Git, Power BI, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2539b8d6d86402e6</t>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Jenkins, GitHub Actions, Git, MySQL, MongoDB, NoSQL, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0d02498cdc4c270f</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Senior Ad Tech Developer</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>USA TODAY Co.</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>10</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Jenkins, GitHub Actions, Git, MySQL, MongoDB, NoSQL, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=353b6365ca90feed</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist Consultant - Agentic Platform (P2393)</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>84.51°</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>10</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Data Scientist, LangChain, Prompt Engineering, MLflow, Databricks, PySpark, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=017ba6c15212df84</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>AI Engineer Intern - Summer 2026 - SoCal</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>CliftonLarsonAllen</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Irvine, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>10</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, Azure ML, Databricks, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=daa07a73d0153f41</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>CrowdStrike AI Security Engineer</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>OR, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>10</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, TensorFlow, PyTorch, CI/CD, Python, R, Bayesian</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0c3320b791c083dc</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>CrowdStrike Container Security Engineer</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>10</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>RAG, LLaMA, Docker, Kubernetes, CI/CD, Jenkins, Git, R, Scala</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2708000b7295021f</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Senior Ad Tech Developer</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>USA TODAY Co.</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>10</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Jenkins, GitHub Actions, Git, MySQL, MongoDB, NoSQL, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=18282ddb27ef1610</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Software Developer / Software Engineer (Dallas/Fort Worth - Hybrid)</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>EnergyBot</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Richardson, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>10</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Terraform, Git, PostgreSQL, MongoDB, Cassandra, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2e5b4ec2f38d6dbf</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>OpenAM</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>10</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, LLaMA, Hugging Face, Prompt Engineering, Python, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8cb8992ca1e4ae03</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Hire And Tech LLC</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>10</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cfe50c81d8576094</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-01.xlsx
+++ b/daily_matches/job_matches_2026-04-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI Engineer-Remote Opportunity</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Answer Financial Inc.</t>
+          <t>Solution Design Group</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,7 +486,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, RAG, Copilot, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch, AWS SageMaker</t>
+          <t>RAG, Kinesis, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Kafka</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,67 +496,67 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f87cb2f562089112</t>
+          <t>https://www.indeed.com/viewjob?jk=3196d29570808b53</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Sr. AI-ML Engineer Data Analytics</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Arkatechture</t>
+          <t>TK Elevator</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.9</v>
+        <v>20</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Prompt Engineering, Cortex, AWS SageMaker, BigQuery, Snowflake, Databricks, BigQuery</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, XGBoost, AWS SageMaker</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-01-04</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7028737452f8f97</t>
+          <t>https://www.indeed.com/viewjob?jk=7147e81270620ea1</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CrowdStrike GenAI Security Engineer</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.8</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Copilot, FAISS, Pinecone, Prompt Engineering, FastAPI, Docker, Kubernetes, AKS</t>
+          <t>Generative AI, RAG, Gemini, Docker, Kubernetes, Jenkins, GitHub Actions, Git, Snowflake, Power BI</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55dc1ff2aee60bf8</t>
+          <t>https://www.indeed.com/viewjob?jk=b169e350c3f599f1</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CrowdStrike Container Security Engineer</t>
+          <t>Senior SIEM Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Newtown Square, PA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka, PostgreSQL</t>
+          <t>RAG, S3, Data Lake, Kinesis, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec3f885a56b1d738</t>
+          <t>https://www.indeed.com/viewjob?jk=e01d27dd76f05ca3</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CrowdStrike Container Security Engineer</t>
+          <t>Advisory Architect, Data/AI Due Diligence- TTS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Boston, NY, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka, PostgreSQL</t>
+          <t>RAG, Glue, Data Lake, Kinesis, Snowflake, Databricks, Kafka, NoSQL, Tableau, Quicksight</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3b70c2a3a58c840</t>
+          <t>https://www.indeed.com/viewjob?jk=e685b1e9ce29a1aa</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CrowdStrike GenAI Security Engineer</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Digipulse Technologies Inc.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, Tableau, Matplotlib, Seaborn</t>
+          <t>Generative AI, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5294f2169087b99c</t>
+          <t>https://www.indeed.com/viewjob?jk=45832e962a1934f9</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Group1001</t>
+          <t>Altom Transport, Inc.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Zionsville, IN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>S3, EC2, Kinesis, Docker, CI/CD, Terraform, Git, Kafka, PostgreSQL, SQL</t>
+          <t>Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Git, MySQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=328132d81f266b40</t>
+          <t>https://www.indeed.com/viewjob?jk=97688623b519e5b3</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>OpenAM</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>REPLY</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, FAISS, Prompt Engineering, FastAPI, Docker, PostgreSQL, MySQL, Python</t>
+          <t>RAG, Synapse, Docker, AKS, Git, Databricks, PySpark, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2798eaba2ec3640</t>
+          <t>https://www.indeed.com/viewjob?jk=b55f03574875963f</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Scientist / Senior Software Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Wolters Kluwer</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, SQL, R</t>
+          <t>Data Scientist, Git, NoSQL, Tableau, Power BI, Matplotlib, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5ae44b7e644f920</t>
+          <t>https://www.indeed.com/viewjob?jk=befc7560d2a7c038</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
+          <t>Partner Engineer - Technology Partnerships</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Sonar</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, TensorFlow, PyTorch, MLflow, Docker, Kubernetes, CI/CD, Hadoop</t>
+          <t>RAG, Copilot, AWS SageMaker, CI/CD, Jenkins, Git, Databricks, Python, R, Java</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b964f7655bcd20af</t>
+          <t>https://www.indeed.com/viewjob?jk=ff0d25fe199be7b2</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Cognos Dashboard Developer</t>
+          <t>Sr. Full Stack Engineer, Web</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Genesys</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Synapse, FastAPI, Docker, CI/CD, Git, PostgreSQL, Python, SQL</t>
+          <t>RAG, Docker, CI/CD, Git, MySQL, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb0be82abd779045</t>
+          <t>https://www.indeed.com/viewjob?jk=04f9b98477334612</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Cognos Dashboard Developer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>University of Colorado</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Aurora, CO, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Synapse, FastAPI, Docker, CI/CD, Git, PostgreSQL, Python, SQL</t>
+          <t>Data Scientist, RAG, LLaMA, TensorFlow, PyTorch, spaCy, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c35b8f5f035a5b2</t>
+          <t>https://www.indeed.com/viewjob?jk=d7f02512666d21b6</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
+          <t>AI Engineer [Trading Analytics &amp; Data Engineering]</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Engineers &amp; Constructors International</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>TensorFlow, PyTorch, S3, EC2, Glue, Docker, Apache Airflow, CI/CD, Jenkins, Terraform</t>
+          <t>AI Engineer, Prompt Engineering, MLflow, CI/CD, Terraform, Databricks, PySpark, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01330f2927806152</t>
+          <t>https://www.indeed.com/viewjob?jk=8e921b3ad3654a7f</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CrowdStrike Container Security Engineer</t>
+          <t>Senior Data Scientist Consultant - Agentic Platform (P2393) New</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>84.51°</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Terraform, Git, Kafka, Python, R</t>
+          <t>Data Scientist, LangChain, Prompt Engineering, MLflow, Databricks, PySpark, Python, SQL, R</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3927505fc5da268f</t>
+          <t>https://www.indeed.com/viewjob?jk=22eae9afb871e165</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Cloud Threat Intelligence Analyst</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Coalfire</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Terraform, Git, Kafka, Python, R</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97457f1413e6a8ff</t>
+          <t>https://www.indeed.com/viewjob?jk=fbaf60714215fab3</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CrowdStrike AI Security Engineer</t>
+          <t>Senior Software Engineer - Java</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Teradata</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, Copilot, Prompt Engineering, FastAPI, CI/CD, Git, Databricks, Python, R</t>
+          <t>Copilot, Docker, CI/CD, Git, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6e92b99aa8a7b69</t>
+          <t>https://www.indeed.com/viewjob?jk=fe83468fdf1e5ede</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>OpenAM</t>
+          <t>GCP Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>TECHNOVAL</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, Copilot, Prompt Engineering, FastAPI, CI/CD, Git, Databricks, Python, R</t>
+          <t>RAG, Dataflow, CI/CD, PostgreSQL, MySQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,567 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ed4889c9b1b3b76</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Intelligence Platform Architect</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, XGBoost, MLflow, Databricks, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6109173d4b2f89d1</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Senior Data Scientist - Digital Intelligence, Device Signals</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Socure</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Carson City, NV, US USA</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, TensorFlow, XGBoost, Git, PySpark, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8464ec9a079b1a80</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>OpenAM</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Docker, Kubernetes, CI/CD, Terraform, MySQL, MongoDB, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=93d9e83869d72aa4</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>OpenAM</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, Prompt Engineering, TensorFlow, CI/CD, Git, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d317cc1d518716e1</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Cognos Business Intelligence Analyst</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>NY, US USA</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer, Generative AI, Databricks, PySpark, Power BI, Python, SQL, R, Optimization, A/B Testing</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ad29a7b3847d7779</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Cognos Business Intelligence Analyst</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>NY, US USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer, Generative AI, Databricks, PySpark, Power BI, Python, SQL, R, Optimization, A/B Testing</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=80bbbb63b208b2dd</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Senior Ad Tech Developer</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>USA TODAY Co.</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Jenkins, GitHub Actions, Git, MySQL, MongoDB, NoSQL, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0d02498cdc4c270f</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Senior Ad Tech Developer</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>USA TODAY Co.</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>10</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Jenkins, GitHub Actions, Git, MySQL, MongoDB, NoSQL, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=353b6365ca90feed</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Senior Data Scientist Consultant - Agentic Platform (P2393)</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>84.51°</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>10</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Data Scientist, LangChain, Prompt Engineering, MLflow, Databricks, PySpark, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=017ba6c15212df84</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>AI Engineer Intern - Summer 2026 - SoCal</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>CliftonLarsonAllen</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Irvine, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>10</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>AI Engineer, Generative AI, RAG, Azure ML, Databricks, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=daa07a73d0153f41</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>CrowdStrike AI Security Engineer</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>OR, US USA</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>10</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>AI Engineer, Machine Learning Engineer, RAG, TensorFlow, PyTorch, CI/CD, Python, R, Bayesian</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0c3320b791c083dc</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>CrowdStrike Container Security Engineer</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>TX, US USA</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>10</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>RAG, LLaMA, Docker, Kubernetes, CI/CD, Jenkins, Git, R, Scala</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2708000b7295021f</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Senior Ad Tech Developer</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>USA TODAY Co.</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>10</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Jenkins, GitHub Actions, Git, MySQL, MongoDB, NoSQL, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=18282ddb27ef1610</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Software Developer / Software Engineer (Dallas/Fort Worth - Hybrid)</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>EnergyBot</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Richardson, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>10</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Terraform, Git, PostgreSQL, MongoDB, Cassandra, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2e5b4ec2f38d6dbf</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>OpenAM</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>10</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Hugging Face, Prompt Engineering, Python, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8cb8992ca1e4ae03</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Data Scientist</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Hire And Tech LLC</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>10</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cfe50c81d8576094</t>
+          <t>https://www.indeed.com/viewjob?jk=8aa372df0d9657b8</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-01.xlsx
+++ b/daily_matches/job_matches_2026-04-01.xlsx
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Sr. AI-ML Engineer Data Analytics</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Solution Design Group</t>
+          <t>TK Elevator</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>21.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Kinesis, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Kafka</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, XGBoost, AWS SageMaker</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,7 +496,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3196d29570808b53</t>
+          <t>https://www.indeed.com/viewjob?jk=0be0a107da6326a2</t>
         </is>
       </c>
     </row>
@@ -513,7 +513,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -526,37 +526,37 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-01-04</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7147e81270620ea1</t>
+          <t>https://www.indeed.com/viewjob?jk=2169bd0539d8ff3a</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Senior Data Engineer, ACVMax</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>ACV Auctions</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>20</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Docker, Kubernetes, Jenkins, GitHub Actions, Git, Snowflake, Power BI</t>
+          <t>Data Scientist, RAG, S3, EC2, Glue, Athena, Redshift, Data Lake, Kinesis, Git</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b169e350c3f599f1</t>
+          <t>https://www.indeed.com/viewjob?jk=f02b64c0c4088808</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior SIEM Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>AdCellerant</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Newtown Square, PA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, S3, Data Lake, Kinesis, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
+          <t>RAG, Copilot, BigQuery, Docker, Git, Snowflake, BigQuery, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e01d27dd76f05ca3</t>
+          <t>https://www.indeed.com/viewjob?jk=56ea99b8f4528836</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Boston, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e685b1e9ce29a1aa</t>
+          <t>https://www.indeed.com/viewjob?jk=330017cf70779a95</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Science and Engineering Associate 2</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Digipulse Technologies Inc.</t>
+          <t>Stanford University</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Stanford, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Generative AI, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, Python</t>
+          <t>Machine Learning Engineer, RAG, Hugging Face, PyTorch, BigQuery, Docker, CI/CD, Git, BigQuery, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45832e962a1934f9</t>
+          <t>https://www.indeed.com/viewjob?jk=d51fcd87a8579df1</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
+          <t>Sr. Software Engineer - Platform</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Altom Transport, Inc.</t>
+          <t>American Innovations Ltd</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Git, MySQL, Python, SQL, R</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, Git, NoSQL, SQL, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97688623b519e5b3</t>
+          <t>https://www.indeed.com/viewjob?jk=1a6071ff182d1660</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>REPLY</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Synapse, Docker, AKS, Git, Databricks, PySpark, Power BI, Python, SQL</t>
+          <t>Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, SQL, R, Java</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b55f03574875963f</t>
+          <t>https://www.indeed.com/viewjob?jk=5419bc0b083078db</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Scientist / Senior Software Engineer</t>
+          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Wolters Kluwer</t>
+          <t>Al Warren Oil Company, Inc.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Bensenville, IL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Scientist, Git, NoSQL, Tableau, Power BI, Matplotlib, Python, SQL, R, Java</t>
+          <t>Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Git, MySQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=befc7560d2a7c038</t>
+          <t>https://www.indeed.com/viewjob?jk=ce538e24964a3f07</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Partner Engineer - Technology Partnerships</t>
+          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Sonar</t>
+          <t>Al Warren Oil Company, Inc.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Copilot, AWS SageMaker, CI/CD, Jenkins, Git, Databricks, Python, R, Java</t>
+          <t>Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Git, MySQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff0d25fe199be7b2</t>
+          <t>https://www.indeed.com/viewjob?jk=979fbd96452ea4ce</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sr. Full Stack Engineer, Web</t>
+          <t>Cloud Data Engineering Operations Specialist</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Genesys</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Docker, CI/CD, Git, MySQL, SQL, R, Java, Scala, Optimization</t>
+          <t>RAG, BigQuery, Dataflow, CI/CD, GitHub Actions, Terraform, Git, BigQuery, Python, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04f9b98477334612</t>
+          <t>https://www.indeed.com/viewjob?jk=672f4d9f4d9b154a</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior MuleSoft Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>University of Colorado</t>
+          <t>Green Irony</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Aurora, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, LLaMA, TensorFlow, PyTorch, spaCy, Git, Python, R, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka, R, Java</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7f02512666d21b6</t>
+          <t>https://www.indeed.com/viewjob?jk=b45e53493b8bdf81</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AI Engineer [Trading Analytics &amp; Data Engineering]</t>
+          <t>AI Innovation and Solutions Engineer - Associate (New York, NY)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Engineers &amp; Constructors International</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AI Engineer, Prompt Engineering, MLflow, CI/CD, Terraform, Databricks, PySpark, SQL, R, Scala</t>
+          <t>RAG, Prompt Engineering, TensorFlow, PyTorch, CI/CD, NoSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e921b3ad3654a7f</t>
+          <t>https://www.indeed.com/viewjob?jk=1084f9324350eb73</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Scientist Consultant - Agentic Platform (P2393) New</t>
+          <t>Sr. Data Scientist</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>84.51°</t>
+          <t>Linde</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>The Woodlands, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, Prompt Engineering, MLflow, Databricks, PySpark, Python, SQL, R</t>
+          <t>Data Scientist, Generative AI, RAG, Git, Tableau, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22eae9afb871e165</t>
+          <t>https://www.indeed.com/viewjob?jk=cfab4fa909564d24</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Coalfire</t>
+          <t>Mad Mobile</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, R, Scala, Optimization</t>
+          <t>RAG, Copilot, Docker, Git, NoSQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbaf60714215fab3</t>
+          <t>https://www.indeed.com/viewjob?jk=961998753b41ddee</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Java</t>
+          <t>System Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Teradata</t>
+          <t>The Wenger Group</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Lancaster, PA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Copilot, Docker, CI/CD, Git, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe83468fdf1e5ede</t>
+          <t>https://www.indeed.com/viewjob?jk=eb283133cba77fc1</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>GCP Cloud Data Engineer</t>
+          <t>Tax-Salt Lake City-Associate-Software Engineering</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>TECHNOVAL</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, Dataflow, CI/CD, PostgreSQL, MySQL, Python, SQL, R, Java</t>
+          <t>Data Scientist, RAG, MongoDB, NoSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8aa372df0d9657b8</t>
+          <t>https://www.indeed.com/viewjob?jk=0f849485bbe552f7</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-01.xlsx
+++ b/daily_matches/job_matches_2026-04-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sr. AI-ML Engineer Data Analytics</t>
+          <t>Software Engineer III - Machine Learning Platform</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>TK Elevator</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>21.1</v>
+        <v>18.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, XGBoost, AWS SageMaker</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, AWS SageMaker, Azure ML, Docker, Kubernetes, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0be0a107da6326a2</t>
+          <t>https://www.indeed.com/viewjob?jk=7c537d5b06db8547</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sr. AI-ML Engineer Data Analytics</t>
+          <t>Software Engineer III - Python AI/ML</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>TK Elevator</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20</v>
+        <v>18.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, XGBoost, AWS SageMaker</t>
+          <t>Data Scientist, RAG, S3, Kinesis, Docker, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2169bd0539d8ff3a</t>
+          <t>https://www.indeed.com/viewjob?jk=6602e90751dfc184</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, ACVMax</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ACV Auctions</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20</v>
+        <v>17.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, EC2, Glue, Athena, Redshift, Data Lake, Kinesis, Git</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, XGBoost, LightGBM, BigQuery, Dataflow, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f02b64c0c4088808</t>
+          <t>https://www.indeed.com/viewjob?jk=2d5d69c2eeb8b1e8</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Agentic AI Architect/Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AdCellerant</t>
+          <t>Rockwell Automation</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>17.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Copilot, BigQuery, Docker, Git, Snowflake, BigQuery, NoSQL, Python, SQL</t>
+          <t>AI Engineer, Generative AI, RAG, Gemini, XGBoost, Docker, CI/CD, Terraform, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56ea99b8f4528836</t>
+          <t>https://www.indeed.com/viewjob?jk=fd28b1ab1e76be27</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Advisory Architect, Data/AI Due Diligence- TTS</t>
+          <t>Senior AI Software Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>West Monroe</t>
+          <t>Trimble</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Lake Oswego, OR, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Glue, Data Lake, Kinesis, Snowflake, Databricks, Kafka, NoSQL, Tableau, Quicksight</t>
+          <t>RAG, Copilot, Prompt Engineering, Docker, Kubernetes, AKS, CI/CD, Terraform, Git, Kafka</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=330017cf70779a95</t>
+          <t>https://www.indeed.com/viewjob?jk=f33e389dcc2b7891</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Science and Engineering Associate 2</t>
+          <t>Cognos Dashboard Developer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Stanford University</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Stanford, CA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, Hugging Face, PyTorch, BigQuery, Docker, CI/CD, Git, BigQuery, Python</t>
+          <t>RAG, Copilot, Synapse, FastAPI, Docker, CI/CD, Git, PostgreSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d51fcd87a8579df1</t>
+          <t>https://www.indeed.com/viewjob?jk=0d7c56aa68fc97c2</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Platform</t>
+          <t>DevOps Engineer with OpenShift Experience</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>American Innovations Ltd</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, Git, NoSQL, SQL, R</t>
+          <t>Generative AI, RAG, Gemini, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, MongoDB</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a6071ff182d1660</t>
+          <t>https://www.indeed.com/viewjob?jk=b83c5b7a778f6743</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Applied AI/ML Associate</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, SQL, R, Java</t>
+          <t>Generative AI, RAG, TensorFlow, PyTorch, Docker, Kubernetes, Snowflake, Databricks, PySpark, Python</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5419bc0b083078db</t>
+          <t>https://www.indeed.com/viewjob?jk=334e7e3aac5e1376</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Al Warren Oil Company, Inc.</t>
+          <t>Worldpay</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bensenville, IL, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Git, MySQL, Python, SQL, R</t>
+          <t>Data Scientist, RAG, S3, Terraform, Snowflake, Databricks, PySpark, Tableau, Power BI, SQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce538e24964a3f07</t>
+          <t>https://www.indeed.com/viewjob?jk=9da22ae229ae1ed1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Al Warren Oil Company, Inc.</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Git, MySQL, Python, SQL, R</t>
+          <t>Generative AI, RAG, BigQuery, CI/CD, Jenkins, Terraform, Git, BigQuery, Python, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=979fbd96452ea4ce</t>
+          <t>https://www.indeed.com/viewjob?jk=07073d5e050e4ba0</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Cloud Data Engineering Operations Specialist</t>
+          <t>Data Software Engineer III- ML</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Dataflow, CI/CD, GitHub Actions, Terraform, Git, BigQuery, Python, R</t>
+          <t>AI Engineer, Data Scientist, RAG, Copilot, Glue, Kinesis, Kubernetes, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=672f4d9f4d9b154a</t>
+          <t>https://www.indeed.com/viewjob?jk=875ef8272fea454a</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior MuleSoft Engineer</t>
+          <t>Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Green Irony</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka, R, Java</t>
+          <t>RAG, Gemini, Copilot, Docker, Kubernetes, Git, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b45e53493b8bdf81</t>
+          <t>https://www.indeed.com/viewjob?jk=13cc452788488eab</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AI Innovation and Solutions Engineer - Associate (New York, NY)</t>
+          <t>Data &amp; Analytics Products &amp; Solutions Specialist</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>L.E.K. Consulting</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, TensorFlow, PyTorch, CI/CD, NoSQL, Python, SQL, R, Java</t>
+          <t>Data Scientist, LangChain, RAG, Prompt Engineering, Azure ML, Git, Snowflake, Python, SQL, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1084f9324350eb73</t>
+          <t>https://www.indeed.com/viewjob?jk=c8861cb9ebb6e9d7</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr. Data Scientist</t>
+          <t>Cognos Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Linde</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>The Woodlands, TX, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Git, Tableau, Power BI, Python, SQL, R, Scala</t>
+          <t>Machine Learning Engineer, Generative AI, Databricks, PySpark, Power BI, Python, SQL, R, Optimization, A/B Testing</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfab4fa909564d24</t>
+          <t>https://www.indeed.com/viewjob?jk=cb93d64bc5d3b638</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Solutions Engineer - Data Visualization</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Mad Mobile</t>
+          <t>SHI International</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Git, NoSQL, SQL, R, Java, Scala</t>
+          <t>RAG, Synapse, Data Lake, Dataflow, Databricks, Power BI, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=961998753b41ddee</t>
+          <t>https://www.indeed.com/viewjob?jk=375b478d9e0a233b</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>System Engineer</t>
+          <t>Senior Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>The Wenger Group</t>
+          <t>ServiceTitan</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Lancaster, PA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Python, R, Scala, Optimization</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,42 +1021,287 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb283133cba77fc1</t>
+          <t>https://www.indeed.com/viewjob?jk=6431593ad2d894f2</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Tax-Salt Lake City-Associate-Software Engineering</t>
+          <t>AI/ML Engineer [REMOTE JOB]</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>BAE Systems USA</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Fort Walton Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, AWS SageMaker, Glue, Data Lake, Docker, Kubernetes, Git, R, Scala</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=984368d3fe8ddfaa</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Data Scientist - Hybrid</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>National Interstate</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Richfield, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, XGBoost, LightGBM, Tableau, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=93b9534ba9996a89</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Applied Researcher</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Ford Motor Company</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Bellevue, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Data Lake, Git, Databricks, PySpark, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ace2c025d62f0928</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>AI Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>VeeRteq Solutions Inc.</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
         <v>10</v>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, MongoDB, NoSQL, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0f849485bbe552f7</t>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>RAG, Gemini, Copilot, AKS, CI/CD, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2077d405c9b18780</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Solutions Engineer - Data Engineering</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>SHI International</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>10</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>RAG, Synapse, Data Lake, Databricks, Power BI, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d72cdd5c1b40ec16</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Senior Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Spark Advisors</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>10</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>RAG, Snowflake, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=778fc0322fd5512a</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Software Engineer AI</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Trimble</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Lake Oswego, OR, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Prompt Engineering, Docker, Kubernetes, AKS, Git, SQL, R</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2c406b170cb001fa</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Data Science Senior Associate - Card Data &amp; Analytics</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Wilmington, DE, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>10</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Git, Hadoop, Tableau, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=990df2794ca5daf3</t>
         </is>
       </c>
     </row>
